--- a/artfynd/A 37307-2021 artfynd.xlsx
+++ b/artfynd/A 37307-2021 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847084</v>
+        <v>119847297</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>57463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +804,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456239</v>
+        <v>456194</v>
       </c>
       <c r="R3" t="n">
-        <v>6946687</v>
+        <v>6946672</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847925</v>
+        <v>119847084</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +930,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456488</v>
+        <v>456239</v>
       </c>
       <c r="R4" t="n">
-        <v>6946525</v>
+        <v>6946687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847441</v>
+        <v>119847925</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1057,14 +1066,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456239</v>
+        <v>456488</v>
       </c>
       <c r="R5" t="n">
-        <v>6946670</v>
+        <v>6946525</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1138,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119847297</v>
+        <v>119847441</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,51 +1163,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456194</v>
+        <v>456239</v>
       </c>
       <c r="R6" t="n">
-        <v>6946672</v>
+        <v>6946670</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 37307-2021 artfynd.xlsx
+++ b/artfynd/A 37307-2021 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847297</v>
+        <v>119847084</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,55 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456194</v>
+        <v>456239</v>
       </c>
       <c r="R3" t="n">
-        <v>6946672</v>
+        <v>6946687</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847084</v>
+        <v>119847925</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,38 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456239</v>
+        <v>456488</v>
       </c>
       <c r="R4" t="n">
-        <v>6946687</v>
+        <v>6946525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847925</v>
+        <v>119847441</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1066,14 +1057,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456488</v>
+        <v>456239</v>
       </c>
       <c r="R5" t="n">
-        <v>6946525</v>
+        <v>6946670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1147,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119847441</v>
+        <v>119847297</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,37 +1154,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456239</v>
+        <v>456194</v>
       </c>
       <c r="R6" t="n">
-        <v>6946670</v>
+        <v>6946672</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 37307-2021 artfynd.xlsx
+++ b/artfynd/A 37307-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119847994</v>
+        <v>119847297</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456524</v>
+        <v>456194</v>
       </c>
       <c r="R2" t="n">
-        <v>6946466</v>
+        <v>6946672</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847925</v>
+        <v>119848020</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +929,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456488</v>
+        <v>456556</v>
       </c>
       <c r="R4" t="n">
-        <v>6946525</v>
+        <v>6946482</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1030,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847441</v>
+        <v>119847835</v>
       </c>
       <c r="B5" t="n">
         <v>57310</v>
@@ -1057,14 +1066,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456239</v>
+        <v>456435</v>
       </c>
       <c r="R5" t="n">
-        <v>6946670</v>
+        <v>6946529</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1138,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119847297</v>
+        <v>119847994</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,51 +1163,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456194</v>
+        <v>456524</v>
       </c>
       <c r="R6" t="n">
-        <v>6946672</v>
+        <v>6946466</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1376,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119848020</v>
+        <v>119847925</v>
       </c>
       <c r="B8" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,42 +1392,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456556</v>
+        <v>456488</v>
       </c>
       <c r="R8" t="n">
-        <v>6946482</v>
+        <v>6946525</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119847835</v>
+        <v>119847441</v>
       </c>
       <c r="B9" t="n">
         <v>57310</v>
@@ -1529,14 +1529,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456435</v>
+        <v>456239</v>
       </c>
       <c r="R9" t="n">
-        <v>6946529</v>
+        <v>6946670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/artfynd/A 37307-2021 artfynd.xlsx
+++ b/artfynd/A 37307-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119847297</v>
+        <v>119847994</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,51 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456194</v>
+        <v>456524</v>
       </c>
       <c r="R2" t="n">
-        <v>6946672</v>
+        <v>6946466</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847084</v>
+        <v>119847297</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>57463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,41 +804,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456239</v>
+        <v>456194</v>
       </c>
       <c r="R3" t="n">
-        <v>6946687</v>
+        <v>6946672</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119848020</v>
+        <v>119847835</v>
       </c>
       <c r="B4" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,42 +934,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456556</v>
+        <v>456435</v>
       </c>
       <c r="R4" t="n">
-        <v>6946482</v>
+        <v>6946529</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847835</v>
+        <v>119847084</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,38 +1047,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456435</v>
+        <v>456239</v>
       </c>
       <c r="R5" t="n">
-        <v>6946529</v>
+        <v>6946687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119847994</v>
+        <v>119847441</v>
       </c>
       <c r="B6" t="n">
         <v>57310</v>
@@ -1181,21 +1181,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456524</v>
+        <v>456239</v>
       </c>
       <c r="R6" t="n">
-        <v>6946466</v>
+        <v>6946670</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119847366</v>
+        <v>119848020</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>57463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,41 +1276,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456224</v>
+        <v>456556</v>
       </c>
       <c r="R7" t="n">
-        <v>6946675</v>
+        <v>6946482</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1493,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119847441</v>
+        <v>119847366</v>
       </c>
       <c r="B9" t="n">
-        <v>57310</v>
+        <v>91852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,25 +1510,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1533,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456239</v>
+        <v>456224</v>
       </c>
       <c r="R9" t="n">
-        <v>6946670</v>
+        <v>6946675</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,12 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 37307-2021 artfynd.xlsx
+++ b/artfynd/A 37307-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119847994</v>
+        <v>119847835</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -709,21 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456524</v>
+        <v>456435</v>
       </c>
       <c r="R2" t="n">
-        <v>6946466</v>
+        <v>6946529</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847297</v>
+        <v>119847441</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,51 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456194</v>
+        <v>456239</v>
       </c>
       <c r="R3" t="n">
-        <v>6946672</v>
+        <v>6946670</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -881,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847835</v>
+        <v>119847925</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -958,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456435</v>
+        <v>456488</v>
       </c>
       <c r="R4" t="n">
-        <v>6946529</v>
+        <v>6946525</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1035,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847084</v>
+        <v>119847994</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,38 +1038,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456239</v>
+        <v>456524</v>
       </c>
       <c r="R5" t="n">
-        <v>6946687</v>
+        <v>6946466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119847441</v>
+        <v>119847297</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,37 +1159,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456239</v>
+        <v>456194</v>
       </c>
       <c r="R6" t="n">
-        <v>6946670</v>
+        <v>6946672</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848020</v>
+        <v>119847084</v>
       </c>
       <c r="B7" t="n">
-        <v>57463</v>
+        <v>91852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,46 +1281,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456556</v>
+        <v>456239</v>
       </c>
       <c r="R7" t="n">
-        <v>6946482</v>
+        <v>6946687</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119847925</v>
+        <v>119847366</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,38 +1393,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456488</v>
+        <v>456224</v>
       </c>
       <c r="R8" t="n">
-        <v>6946525</v>
+        <v>6946675</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,12 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119847366</v>
+        <v>119848020</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>57463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,41 +1505,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456224</v>
+        <v>456556</v>
       </c>
       <c r="R9" t="n">
-        <v>6946675</v>
+        <v>6946482</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 37307-2021 artfynd.xlsx
+++ b/artfynd/A 37307-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119847835</v>
+        <v>119847297</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456435</v>
+        <v>456194</v>
       </c>
       <c r="R2" t="n">
-        <v>6946529</v>
+        <v>6946672</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847441</v>
+        <v>119847366</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>91870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456239</v>
+        <v>456224</v>
       </c>
       <c r="R3" t="n">
-        <v>6946670</v>
+        <v>6946675</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847925</v>
+        <v>119847441</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,14 +949,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456488</v>
+        <v>456239</v>
       </c>
       <c r="R4" t="n">
-        <v>6946525</v>
+        <v>6946670</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1029,7 +1033,7 @@
         <v>119847994</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1143,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119847297</v>
+        <v>119847925</v>
       </c>
       <c r="B6" t="n">
-        <v>57463</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,51 +1163,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456194</v>
+        <v>456488</v>
       </c>
       <c r="R6" t="n">
-        <v>6946672</v>
+        <v>6946525</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1232,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,7 +1267,7 @@
         <v>119847084</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119847366</v>
+        <v>119847835</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,38 +1388,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456224</v>
+        <v>456435</v>
       </c>
       <c r="R8" t="n">
-        <v>6946675</v>
+        <v>6946529</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,7 +1496,7 @@
         <v>119848020</v>
       </c>
       <c r="B9" t="n">
-        <v>57463</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 37307-2021 artfynd.xlsx
+++ b/artfynd/A 37307-2021 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847366</v>
+        <v>119847441</v>
       </c>
       <c r="B3" t="n">
-        <v>91870</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456224</v>
+        <v>456239</v>
       </c>
       <c r="R3" t="n">
-        <v>6946675</v>
+        <v>6946670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847441</v>
+        <v>119847994</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -947,16 +952,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456239</v>
+        <v>456524</v>
       </c>
       <c r="R4" t="n">
-        <v>6946670</v>
+        <v>6946466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847994</v>
+        <v>119847366</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>91870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,43 +1047,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456524</v>
+        <v>456224</v>
       </c>
       <c r="R5" t="n">
-        <v>6946466</v>
+        <v>6946675</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 37307-2021 artfynd.xlsx
+++ b/artfynd/A 37307-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119847297</v>
+        <v>119847925</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,51 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456194</v>
+        <v>456488</v>
       </c>
       <c r="R2" t="n">
-        <v>6946672</v>
+        <v>6946525</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847441</v>
+        <v>119847366</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>91870</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +804,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456239</v>
+        <v>456224</v>
       </c>
       <c r="R3" t="n">
-        <v>6946670</v>
+        <v>6946675</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847994</v>
+        <v>119847835</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -952,21 +938,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456524</v>
+        <v>456435</v>
       </c>
       <c r="R4" t="n">
-        <v>6946466</v>
+        <v>6946529</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847366</v>
+        <v>119847441</v>
       </c>
       <c r="B5" t="n">
-        <v>91870</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,25 +1033,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456224</v>
+        <v>456239</v>
       </c>
       <c r="R5" t="n">
-        <v>6946675</v>
+        <v>6946670</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119847925</v>
+        <v>119847994</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1181,16 +1172,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456488</v>
+        <v>456524</v>
       </c>
       <c r="R6" t="n">
-        <v>6946525</v>
+        <v>6946466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119847084</v>
+        <v>119848020</v>
       </c>
       <c r="B7" t="n">
-        <v>91870</v>
+        <v>57473</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,41 +1267,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456239</v>
+        <v>456556</v>
       </c>
       <c r="R7" t="n">
-        <v>6946687</v>
+        <v>6946482</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119847835</v>
+        <v>119847297</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,37 +1388,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456435</v>
+        <v>456194</v>
       </c>
       <c r="R8" t="n">
-        <v>6946529</v>
+        <v>6946672</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119848020</v>
+        <v>119847084</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>91870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,46 +1510,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456556</v>
+        <v>456239</v>
       </c>
       <c r="R9" t="n">
-        <v>6946482</v>
+        <v>6946687</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 37307-2021 artfynd.xlsx
+++ b/artfynd/A 37307-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119847925</v>
+        <v>119847994</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -709,16 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456488</v>
+        <v>456524</v>
       </c>
       <c r="R2" t="n">
-        <v>6946525</v>
+        <v>6946466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119847366</v>
+        <v>119847297</v>
       </c>
       <c r="B3" t="n">
-        <v>91870</v>
+        <v>57473</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +804,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456224</v>
+        <v>456194</v>
       </c>
       <c r="R3" t="n">
-        <v>6946675</v>
+        <v>6946672</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119847835</v>
+        <v>119848020</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,37 +934,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456435</v>
+        <v>456556</v>
       </c>
       <c r="R4" t="n">
-        <v>6946529</v>
+        <v>6946482</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847441</v>
+        <v>119847366</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>91870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,25 +1047,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456239</v>
+        <v>456224</v>
       </c>
       <c r="R5" t="n">
-        <v>6946670</v>
+        <v>6946675</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119847994</v>
+        <v>119847835</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1172,21 +1181,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456524</v>
+        <v>456435</v>
       </c>
       <c r="R6" t="n">
-        <v>6946466</v>
+        <v>6946529</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1232,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119848020</v>
+        <v>119847441</v>
       </c>
       <c r="B7" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,42 +1280,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456556</v>
+        <v>456239</v>
       </c>
       <c r="R7" t="n">
-        <v>6946482</v>
+        <v>6946670</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119847297</v>
+        <v>119847084</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>91870</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,55 +1393,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456194</v>
+        <v>456239</v>
       </c>
       <c r="R8" t="n">
-        <v>6946672</v>
+        <v>6946687</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119847084</v>
+        <v>119847925</v>
       </c>
       <c r="B9" t="n">
-        <v>91870</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,38 +1505,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456239</v>
+        <v>456488</v>
       </c>
       <c r="R9" t="n">
-        <v>6946687</v>
+        <v>6946525</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1578,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 37307-2021 artfynd.xlsx
+++ b/artfynd/A 37307-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119847994</v>
+        <v>119847925</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -709,21 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456524</v>
+        <v>456488</v>
       </c>
       <c r="R2" t="n">
-        <v>6946466</v>
+        <v>6946525</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119848020</v>
+        <v>119847441</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,42 +934,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skålan, Skålan, Jmt</t>
+          <t>Mobäcken, Mobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456556</v>
+        <v>456239</v>
       </c>
       <c r="R4" t="n">
-        <v>6946482</v>
+        <v>6946670</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack, spår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119847366</v>
+        <v>119847994</v>
       </c>
       <c r="B5" t="n">
-        <v>91870</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,38 +1047,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mobäcken, Mobäcken, Jmt</t>
+          <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456224</v>
+        <v>456524</v>
       </c>
       <c r="R5" t="n">
-        <v>6946675</v>
+        <v>6946466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1125,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1152,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119847835</v>
+        <v>119848020</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,37 +1168,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skålan, Skålan, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456435</v>
+        <v>456556</v>
       </c>
       <c r="R6" t="n">
-        <v>6946529</v>
+        <v>6946482</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1222,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119847441</v>
+        <v>119847084</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>91870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,25 +1281,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,7 +1312,7 @@
         <v>456239</v>
       </c>
       <c r="R7" t="n">
-        <v>6946670</v>
+        <v>6946687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack, spår</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119847084</v>
+        <v>119847366</v>
       </c>
       <c r="B8" t="n">
         <v>91870</v>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456239</v>
+        <v>456224</v>
       </c>
       <c r="R8" t="n">
-        <v>6946687</v>
+        <v>6946675</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119847925</v>
+        <v>119847835</v>
       </c>
       <c r="B9" t="n">
         <v>57320</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456488</v>
+        <v>456435</v>
       </c>
       <c r="R9" t="n">
-        <v>6946525</v>
+        <v>6946529</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
